--- a/sheets/조재수대금교본/검수/바람의 소원.xlsx
+++ b/sheets/조재수대금교본/검수/바람의 소원.xlsx
@@ -4438,13 +4438,13 @@
       <c r="C3" s="22"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="E3" s="22"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="G3" s="22"/>
@@ -4620,7 +4620,6 @@
       <c r="D6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-‹
 㴌汰</t>
         </is>
       </c>
@@ -4628,7 +4627,6 @@
       <c r="F6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-‹
 㴌汰</t>
         </is>
       </c>
@@ -4671,7 +4669,6 @@
       <c r="R6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-‹
 㒣</t>
         </is>
       </c>
@@ -4732,12 +4729,7 @@
     </row>
     <row r="8" ht="91.25" customHeight="true">
       <c r="A8" s="0"/>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="B8" s="21"/>
       <c r="C8" s="25"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
@@ -4795,8 +4787,7 @@
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
-‹</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="C10" s="26"/>
@@ -4921,7 +4912,6 @@
       <c r="D12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-‹
 㳞</t>
         </is>
       </c>
@@ -4982,8 +4972,7 @@
       <c r="C13" s="25"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="E13" s="25"/>
@@ -4996,8 +4985,7 @@
       <c r="G13" s="25"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
-‹</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="I13" s="25"/>
@@ -5017,8 +5005,7 @@
       <c r="M13" s="25"/>
       <c r="N13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="O13" s="25"/>
@@ -5031,8 +5018,7 @@
       <c r="Q13" s="25"/>
       <c r="R13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="S13" s="25"/>
@@ -5051,8 +5037,7 @@
       <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-應
-‹</t>
+應</t>
         </is>
       </c>
       <c r="G14" s="26"/>
@@ -5184,19 +5169,11 @@
       <c r="K17" s="25"/>
       <c r="L17" s="21"/>
       <c r="M17" s="25"/>
-      <c r="N17" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N17" s="21"/>
       <c r="O17" s="25"/>
       <c r="P17" s="21"/>
       <c r="Q17" s="25"/>
-      <c r="R17" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R17" s="21"/>
       <c r="S17" s="25"/>
     </row>
     <row r="18" ht="91.25" customHeight="true">

--- a/sheets/조재수대금교본/검수/바람의 소원.xlsx
+++ b/sheets/조재수대금교본/검수/바람의 소원.xlsx
@@ -4438,13 +4438,13 @@
       <c r="C3" s="22"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ</t>
         </is>
       </c>
       <c r="E3" s="22"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ</t>
         </is>
       </c>
       <c r="G3" s="22"/>
@@ -4729,7 +4729,11 @@
     </row>
     <row r="8" ht="91.25" customHeight="true">
       <c r="A8" s="0"/>
-      <c r="B8" s="21"/>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="C8" s="25"/>
       <c r="D8" s="21" t="inlineStr">
         <is>

--- a/sheets/조재수대금교본/검수/바람의 소원.xlsx
+++ b/sheets/조재수대금교본/검수/바람의 소원.xlsx
@@ -4380,30 +4380,30 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="81.63" customHeight="true">
+    <row r="2" ht="71.43" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="91.25" customHeight="true">
+    <row r="3" ht="79.8" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
       </c>
       <c r="S3" s="24"/>
     </row>
-    <row r="4" ht="91.25" customHeight="true">
+    <row r="4" ht="79.8" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="S4" s="25"/>
     </row>
-    <row r="5" ht="91.25" customHeight="true">
+    <row r="5" ht="79.8" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="S5" s="25"/>
     </row>
-    <row r="6" ht="91.25" customHeight="true">
+    <row r="6" ht="79.8" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="26"/>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="S6" s="27"/>
     </row>
-    <row r="7" ht="91.25" customHeight="true">
+    <row r="7" ht="79.8" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="22"/>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="S7" s="22"/>
     </row>
-    <row r="8" ht="91.25" customHeight="true">
+    <row r="8" ht="79.8" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
       <c r="R8" s="21"/>
       <c r="S8" s="25"/>
     </row>
-    <row r="9" ht="91.25" customHeight="true">
+    <row r="9" ht="79.8" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
       <c r="R9" s="21"/>
       <c r="S9" s="25"/>
     </row>
-    <row r="10" ht="91.25" customHeight="true">
+    <row r="10" ht="79.8" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="S10" s="26"/>
     </row>
-    <row r="11" ht="91.25" customHeight="true">
+    <row r="11" ht="79.8" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="S11" s="22"/>
     </row>
-    <row r="12" ht="91.25" customHeight="true">
+    <row r="12" ht="79.8" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="25"/>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="S12" s="25"/>
     </row>
-    <row r="13" ht="91.25" customHeight="true">
+    <row r="13" ht="79.8" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="25"/>
@@ -5027,7 +5027,7 @@
       </c>
       <c r="S13" s="25"/>
     </row>
-    <row r="14" ht="91.25" customHeight="true">
+    <row r="14" ht="79.8" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="26"/>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="S14" s="26"/>
     </row>
-    <row r="15" ht="91.25" customHeight="true">
+    <row r="15" ht="79.8" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -5134,7 +5134,7 @@
       <c r="R15" s="21"/>
       <c r="S15" s="22"/>
     </row>
-    <row r="16" ht="91.25" customHeight="true">
+    <row r="16" ht="79.8" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="25"/>
@@ -5155,7 +5155,7 @@
       <c r="R16" s="21"/>
       <c r="S16" s="25"/>
     </row>
-    <row r="17" ht="91.25" customHeight="true">
+    <row r="17" ht="79.8" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
       <c r="R17" s="21"/>
       <c r="S17" s="25"/>
     </row>
-    <row r="18" ht="91.25" customHeight="true">
+    <row r="18" ht="79.8" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="26"/>
@@ -5246,6 +5246,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
 </worksheet>
 </file>